--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N136_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N136_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>75.3439236930748</v>
+        <v>12.24338760012466</v>
       </c>
       <c r="D2" t="n">
-        <v>29.65197225562807</v>
+        <v>4.818445491539561</v>
       </c>
       <c r="E2" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F2" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.332474247066869</v>
+        <v>0.8665270651483662</v>
       </c>
       <c r="D3" t="n">
-        <v>5.136159164584959</v>
+        <v>0.8346258642450559</v>
       </c>
       <c r="E3" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F3" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.38678771676129</v>
+        <v>9.16285300397371</v>
       </c>
       <c r="D4" t="n">
-        <v>34.70909242643222</v>
+        <v>5.640227519295236</v>
       </c>
       <c r="E4" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F4" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.4669322295963</v>
+        <v>9.988376487309399</v>
       </c>
       <c r="D5" t="n">
-        <v>38.74847667256668</v>
+        <v>6.296627459292086</v>
       </c>
       <c r="E5" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F5" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>47.25632611412119</v>
+        <v>7.679152993544693</v>
       </c>
       <c r="D6" t="n">
-        <v>27.88250461887537</v>
+        <v>4.530907000567248</v>
       </c>
       <c r="E6" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F6" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.8190668649989</v>
+        <v>6.308098365562321</v>
       </c>
       <c r="D7" t="n">
-        <v>28.42298887760906</v>
+        <v>4.618735692611473</v>
       </c>
       <c r="E7" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F7" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.67114650518788</v>
+        <v>9.20906130709303</v>
       </c>
       <c r="D8" t="n">
-        <v>31.72844850358183</v>
+        <v>5.155872881832048</v>
       </c>
       <c r="E8" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F8" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>42.50135179444355</v>
+        <v>6.906469666597078</v>
       </c>
       <c r="D9" t="n">
-        <v>19.6391049807379</v>
+        <v>3.19135455936991</v>
       </c>
       <c r="E9" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F9" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.81460521037064</v>
+        <v>6.30737334668523</v>
       </c>
       <c r="D10" t="n">
-        <v>38.76459466295395</v>
+        <v>6.299246632730017</v>
       </c>
       <c r="E10" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F10" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.33713024772381</v>
+        <v>3.792283665255118</v>
       </c>
       <c r="D11" t="n">
-        <v>21.70709087455504</v>
+        <v>3.527402267115194</v>
       </c>
       <c r="E11" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F11" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>21.44037858496879</v>
+        <v>3.484061520057429</v>
       </c>
       <c r="D12" t="n">
-        <v>22.59301760377405</v>
+        <v>3.671365360613284</v>
       </c>
       <c r="E12" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F12" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>53.63563372176013</v>
+        <v>8.715790479786021</v>
       </c>
       <c r="D13" t="n">
-        <v>51.89404592706254</v>
+        <v>8.432782463147664</v>
       </c>
       <c r="E13" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F13" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.16106209938867</v>
+        <v>3.60117259115066</v>
       </c>
       <c r="D14" t="n">
-        <v>33.58116204726162</v>
+        <v>5.456938832680014</v>
       </c>
       <c r="E14" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F14" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>21.88024597460424</v>
+        <v>3.555539970873189</v>
       </c>
       <c r="D15" t="n">
-        <v>2.896215541431213</v>
+        <v>0.4706350254825722</v>
       </c>
       <c r="E15" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F15" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14.60974253195536</v>
+        <v>2.374083161442747</v>
       </c>
       <c r="D16" t="n">
-        <v>18.61674815700574</v>
+        <v>3.025221575513433</v>
       </c>
       <c r="E16" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F16" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>35.09135421691514</v>
+        <v>5.702345060248711</v>
       </c>
       <c r="D17" t="n">
-        <v>54.10277010538545</v>
+        <v>8.791700142125135</v>
       </c>
       <c r="E17" t="n">
-        <v>18.71417441927506</v>
+        <v>3.041053343132198</v>
       </c>
       <c r="F17" t="n">
-        <v>13.57226046305332</v>
+        <v>2.205492325246164</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
